--- a/SAMPLE.xlsx
+++ b/SAMPLE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Server-Pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C894C337-E3C5-46E2-9639-E3F841CC3BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -52,7 +52,7 @@
     <t>1.Payment requested within 15 DAYS</t>
   </si>
   <si>
-    <t>For SAASTHA ENGINEERING WORKS</t>
+    <t>For EXAMPLE ENGINEERING WORKS</t>
   </si>
   <si>
     <t>Terms &amp; Conditions:</t>
@@ -73,13 +73,13 @@
     <t>Total Amount After Tax</t>
   </si>
   <si>
-    <t>IFSC CODE:FDRL0001775</t>
+    <t>IFSC CODE:EXAM0000001</t>
   </si>
   <si>
     <t>Total Amount :GST</t>
   </si>
   <si>
-    <t>BRANCH: LOUISWADI THANE</t>
+    <t>BRANCH: EXAMPLE BRANCH</t>
   </si>
   <si>
     <t>-</t>
@@ -88,13 +88,13 @@
     <t>ADD:  IGST</t>
   </si>
   <si>
-    <t>ACCOUNT NUMBER:17750200004019</t>
+    <t>ACCOUNT NUMBER:00000000123456</t>
   </si>
   <si>
     <t>ADD:  SGST</t>
   </si>
   <si>
-    <t>Bank Name: THE FEDERAL BANK LTD</t>
+    <t>Bank Name: EXAMPLE BANK LTD</t>
   </si>
   <si>
     <t>ADD:  CGST</t>
@@ -142,13 +142,13 @@
     <t>Transporter Mode</t>
   </si>
   <si>
-    <t>Party's GST No.27AAACH1784M1Z9</t>
+    <t>Party's GST No.27AAACD5678E1Z9</t>
   </si>
   <si>
     <t>STATE CODE:27</t>
   </si>
   <si>
-    <t xml:space="preserve">THANE                          </t>
+    <t xml:space="preserve">EXAMPLE CITY                   </t>
   </si>
   <si>
     <t>PLACE OF SUPPLY</t>
@@ -181,19 +181,19 @@
     <t>Details of Receipient (Billed To)</t>
   </si>
   <si>
-    <t>Email (1):saastha01@gmail.com Email(2): saasthaenggworks2011@gmail.com Mob.9969434432 &amp; 9969142688</t>
-  </si>
-  <si>
-    <t>Office Address: Unit No.1,GalaNo.2 &amp; 3,NearITI Circle,Road No.28,Kailash Nagar,Wagle Estate,Thane - 400 604,State- Maharashtra</t>
-  </si>
-  <si>
-    <t>GST No.27AAMPE1857D2ZT  MSME NO.UDYAM-MH-33-0054711</t>
+    <t>Email (1):example1@example.com Email(2): example2@example.com Mob.9000000001 &amp; 9000000002</t>
+  </si>
+  <si>
+    <t>Office Address: Unit No.1,GalaNo.2 &amp; 3,NearExample Circle,Road No.28,Example Nagar,Example Estate,Example City - 000 001,State- Maharashtra</t>
+  </si>
+  <si>
+    <t>GST No.27AAAPE1234F1Z9  MSME NO.UDYAM-MH-00-0000001</t>
   </si>
   <si>
     <t>Manufacturing Traders of Machinery,Precision Job Works &amp; Industrial Products</t>
   </si>
   <si>
-    <t>SAASTHA ENGINEERING WORKS</t>
+    <t>EXAMPLE ENGINEERING WORKS</t>
   </si>
   <si>
     <t>TAX INVOICE</t>
@@ -226,10 +226,10 @@
     <t>1.Payment requested within 40 DAYS</t>
   </si>
   <si>
-    <t>MH 04 JQ 4172</t>
-  </si>
-  <si>
-    <t>SEW/274/2026-27</t>
+    <t>MH 00 EX 0000</t>
+  </si>
+  <si>
+    <t>FIX/274/2026-27</t>
   </si>
   <si>
     <t>5L TP CL COOKER BODY 2ND DRAW TOOL DIE ASSY FOR TR</t>
@@ -241,16 +241,16 @@
     <t>Total Invoice Amount in Words:- FIFTEEN THOUSAND SIX HUNDRED AND THIRTY FIVE ONLY</t>
   </si>
   <si>
-    <t>WT/SO/2602478</t>
-  </si>
-  <si>
-    <t>MH04 JQ 4172</t>
-  </si>
-  <si>
-    <t>SEW/292/2026-27</t>
-  </si>
-  <si>
-    <t>WT/PO/CP/600758</t>
+    <t>WT/SO/9000001</t>
+  </si>
+  <si>
+    <t>MH00 EX 0000</t>
+  </si>
+  <si>
+    <t>FIX/292/2026-27</t>
+  </si>
+  <si>
+    <t>WT/PO/CP/9000001</t>
   </si>
   <si>
     <t>2L RICE COOKER BODY DRAW DIE CI [3011821]</t>
